--- a/docs/Mapping_casi_uso/nascita/Dic_Nasc_999.xlsx
+++ b/docs/Mapping_casi_uso/nascita/Dic_Nasc_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="123">
   <si>
     <t>Sezione</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Madre</t>
@@ -433,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -746,62 +752,62 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>46</v>
@@ -810,21 +816,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>48</v>
@@ -833,12 +839,12 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>49</v>
@@ -847,7 +853,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>50</v>
@@ -856,12 +862,12 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>51</v>
@@ -870,7 +876,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>52</v>
@@ -879,12 +885,12 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>53</v>
@@ -893,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>54</v>
@@ -902,21 +908,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>56</v>
@@ -925,12 +931,12 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>57</v>
@@ -939,7 +945,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>58</v>
@@ -948,12 +954,12 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>59</v>
@@ -962,7 +968,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
@@ -971,12 +977,12 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
@@ -985,7 +991,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -994,12 +1000,12 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
@@ -1008,7 +1014,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1017,21 +1023,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1040,12 +1046,12 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
@@ -1054,7 +1060,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1063,21 +1069,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1086,12 +1092,12 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -1100,7 +1106,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1109,12 +1115,12 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
@@ -1123,7 +1129,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1132,12 +1138,12 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
@@ -1146,7 +1152,7 @@
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1155,12 +1161,12 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
@@ -1169,7 +1175,7 @@
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1178,12 +1184,12 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
@@ -1192,7 +1198,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1201,12 +1207,12 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
@@ -1215,7 +1221,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1224,12 +1230,12 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
@@ -1238,7 +1244,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1247,12 +1253,12 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
@@ -1261,7 +1267,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1270,21 +1276,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1293,12 +1299,12 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
@@ -1307,7 +1313,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1316,21 +1322,21 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1339,12 +1345,12 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
@@ -1353,7 +1359,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1362,12 +1368,12 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
@@ -1376,7 +1382,7 @@
         <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1385,12 +1391,12 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
@@ -1399,7 +1405,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1408,12 +1414,12 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
@@ -1422,7 +1428,7 @@
         <v>25</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1431,67 +1437,67 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>46</v>
@@ -1500,21 +1506,21 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>48</v>
@@ -1523,12 +1529,12 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>49</v>
@@ -1537,7 +1543,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>50</v>
@@ -1546,12 +1552,12 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>51</v>
@@ -1560,7 +1566,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>52</v>
@@ -1569,12 +1575,12 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>53</v>
@@ -1583,7 +1589,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>54</v>
@@ -1592,21 +1598,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>56</v>
@@ -1615,12 +1621,12 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>57</v>
@@ -1629,7 +1635,7 @@
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>58</v>
@@ -1638,12 +1644,12 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>59</v>
@@ -1652,7 +1658,7 @@
         <v>25</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>60</v>
@@ -1661,12 +1667,12 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>61</v>
@@ -1675,7 +1681,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>62</v>
@@ -1684,12 +1690,12 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>63</v>
@@ -1698,7 +1704,7 @@
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>64</v>
@@ -1707,21 +1713,21 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>66</v>
@@ -1730,12 +1736,12 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>67</v>
@@ -1744,7 +1750,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>68</v>
@@ -1753,21 +1759,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>70</v>
@@ -1776,12 +1782,12 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>71</v>
@@ -1790,7 +1796,7 @@
         <v>25</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>72</v>
@@ -1799,12 +1805,12 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>73</v>
@@ -1813,7 +1819,7 @@
         <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>74</v>
@@ -1822,12 +1828,12 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>75</v>
@@ -1836,7 +1842,7 @@
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>76</v>
@@ -1845,12 +1851,12 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>77</v>
@@ -1859,7 +1865,7 @@
         <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>78</v>
@@ -1868,12 +1874,12 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>79</v>
@@ -1882,7 +1888,7 @@
         <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>80</v>
@@ -1891,12 +1897,12 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>81</v>
@@ -1905,7 +1911,7 @@
         <v>25</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>82</v>
@@ -1914,12 +1920,12 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>83</v>
@@ -1928,7 +1934,7 @@
         <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>84</v>
@@ -1937,12 +1943,12 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>85</v>
@@ -1951,7 +1957,7 @@
         <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>86</v>
@@ -1960,21 +1966,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>88</v>
@@ -1983,12 +1989,12 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>89</v>
@@ -1997,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>90</v>
@@ -2006,21 +2012,21 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>92</v>
@@ -2029,12 +2035,12 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>93</v>
@@ -2043,7 +2049,7 @@
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>94</v>
@@ -2052,12 +2058,12 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>95</v>
@@ -2066,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>96</v>
@@ -2075,12 +2081,12 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>97</v>
@@ -2089,7 +2095,7 @@
         <v>25</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>98</v>
@@ -2098,12 +2104,12 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>99</v>
@@ -2112,7 +2118,7 @@
         <v>25</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>100</v>
@@ -2121,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74">
@@ -2129,7 +2135,7 @@
         <v>103</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>25</v>
@@ -2138,50 +2144,50 @@
         <v>104</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>46</v>
@@ -2190,12 +2196,12 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>47</v>
@@ -2204,7 +2210,7 @@
         <v>25</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>48</v>
@@ -2213,12 +2219,12 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>49</v>
@@ -2227,7 +2233,7 @@
         <v>25</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>50</v>
@@ -2236,12 +2242,12 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>51</v>
@@ -2250,7 +2256,7 @@
         <v>25</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>52</v>
@@ -2259,12 +2265,12 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>53</v>
@@ -2273,7 +2279,7 @@
         <v>25</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>54</v>
@@ -2282,12 +2288,12 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>55</v>
@@ -2296,7 +2302,7 @@
         <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>56</v>
@@ -2305,12 +2311,12 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>57</v>
@@ -2319,7 +2325,7 @@
         <v>25</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>58</v>
@@ -2328,12 +2334,12 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>59</v>
@@ -2342,7 +2348,7 @@
         <v>25</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>60</v>
@@ -2351,12 +2357,12 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>61</v>
@@ -2365,7 +2371,7 @@
         <v>25</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>62</v>
@@ -2374,12 +2380,12 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>63</v>
@@ -2388,7 +2394,7 @@
         <v>25</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>64</v>
@@ -2397,12 +2403,12 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>65</v>
@@ -2411,7 +2417,7 @@
         <v>25</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>66</v>
@@ -2420,12 +2426,12 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>67</v>
@@ -2434,7 +2440,7 @@
         <v>25</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>68</v>
@@ -2443,12 +2449,12 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>69</v>
@@ -2457,7 +2463,7 @@
         <v>25</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>70</v>
@@ -2466,12 +2472,12 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>71</v>
@@ -2480,7 +2486,7 @@
         <v>25</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>72</v>
@@ -2489,12 +2495,12 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>73</v>
@@ -2503,7 +2509,7 @@
         <v>25</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>74</v>
@@ -2512,12 +2518,12 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>75</v>
@@ -2526,7 +2532,7 @@
         <v>25</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>76</v>
@@ -2535,12 +2541,12 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>77</v>
@@ -2549,7 +2555,7 @@
         <v>25</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>78</v>
@@ -2558,12 +2564,12 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>79</v>
@@ -2572,7 +2578,7 @@
         <v>25</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>80</v>
@@ -2581,12 +2587,12 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>81</v>
@@ -2595,7 +2601,7 @@
         <v>25</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>82</v>
@@ -2604,12 +2610,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>83</v>
@@ -2618,7 +2624,7 @@
         <v>25</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>84</v>
@@ -2627,12 +2633,12 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>85</v>
@@ -2641,7 +2647,7 @@
         <v>25</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>86</v>
@@ -2650,12 +2656,12 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>87</v>
@@ -2664,7 +2670,7 @@
         <v>25</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>88</v>
@@ -2673,12 +2679,12 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>89</v>
@@ -2687,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>90</v>
@@ -2696,12 +2702,12 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>91</v>
@@ -2710,7 +2716,7 @@
         <v>25</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>92</v>
@@ -2719,7 +2725,7 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="100">
@@ -2727,7 +2733,7 @@
         <v>105</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>25</v>
@@ -2736,30 +2742,30 @@
         <v>106</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2770,19 +2776,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2793,7 +2799,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>109</v>
@@ -2816,19 +2822,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -2839,16 +2845,16 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>48</v>
@@ -2862,7 +2868,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>49</v>
@@ -2871,7 +2877,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>50</v>
@@ -2885,19 +2891,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -2908,7 +2914,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>113</v>
@@ -2931,19 +2937,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -2954,16 +2960,16 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>54</v>
@@ -2977,16 +2983,16 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>56</v>
@@ -3000,16 +3006,16 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>58</v>
@@ -3023,16 +3029,16 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>60</v>
@@ -3046,7 +3052,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>61</v>
@@ -3055,7 +3061,7 @@
         <v>25</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>62</v>
@@ -3069,19 +3075,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3092,19 +3098,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3115,7 +3121,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>95</v>
@@ -3124,7 +3130,7 @@
         <v>25</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>96</v>
@@ -3138,7 +3144,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>97</v>
@@ -3147,7 +3153,7 @@
         <v>25</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>98</v>
@@ -3161,7 +3167,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>99</v>
@@ -3170,7 +3176,7 @@
         <v>25</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>100</v>
@@ -3184,24 +3190,47 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C120" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D121" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G120" s="2" t="s">
+      <c r="E121" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/nascita/Dic_Nasc_999.xlsx
+++ b/docs/Mapping_casi_uso/nascita/Dic_Nasc_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="129">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Tipologia Nascita</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>evento.datiDiNascita</t>
@@ -451,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -510,63 +516,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -575,90 +581,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>29</v>
@@ -667,21 +673,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>31</v>
@@ -690,21 +696,21 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -713,12 +719,12 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>34</v>
@@ -727,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>35</v>
@@ -736,21 +742,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>37</v>
@@ -759,21 +765,21 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>39</v>
@@ -782,67 +788,67 @@
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="F16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>48</v>
@@ -851,12 +857,12 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>49</v>
@@ -865,7 +871,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>50</v>
@@ -874,21 +880,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>52</v>
@@ -897,21 +903,21 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>54</v>
@@ -920,12 +926,12 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>55</v>
@@ -934,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>56</v>
@@ -943,21 +949,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>58</v>
@@ -966,21 +972,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
@@ -989,21 +995,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>62</v>
@@ -1012,21 +1018,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -1035,21 +1041,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>66</v>
@@ -1058,21 +1064,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>68</v>
@@ -1081,21 +1087,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -1104,12 +1110,12 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -1118,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1127,21 +1133,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1150,21 +1156,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1173,21 +1179,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
@@ -1196,21 +1202,21 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
@@ -1219,21 +1225,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>82</v>
@@ -1242,21 +1248,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>84</v>
@@ -1265,21 +1271,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>86</v>
@@ -1288,21 +1294,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>88</v>
@@ -1311,21 +1317,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>90</v>
@@ -1334,21 +1340,21 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>92</v>
@@ -1357,12 +1363,12 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>93</v>
@@ -1371,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>94</v>
@@ -1380,21 +1386,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>96</v>
@@ -1403,21 +1409,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>98</v>
@@ -1426,21 +1432,21 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>100</v>
@@ -1449,21 +1455,21 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>102</v>
@@ -1472,21 +1478,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>104</v>
@@ -1495,21 +1501,21 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>106</v>
@@ -1518,67 +1524,67 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>48</v>
@@ -1587,12 +1593,12 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>49</v>
@@ -1601,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>50</v>
@@ -1610,21 +1616,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>52</v>
@@ -1633,21 +1639,21 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>54</v>
@@ -1656,12 +1662,12 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>55</v>
@@ -1670,7 +1676,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>56</v>
@@ -1679,21 +1685,21 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>58</v>
@@ -1702,21 +1708,21 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>60</v>
@@ -1725,21 +1731,21 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>62</v>
@@ -1748,21 +1754,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>64</v>
@@ -1771,21 +1777,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>66</v>
@@ -1794,21 +1800,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>68</v>
@@ -1817,21 +1823,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>70</v>
@@ -1840,12 +1846,12 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>71</v>
@@ -1854,7 +1860,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>72</v>
@@ -1863,21 +1869,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>74</v>
@@ -1886,21 +1892,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>76</v>
@@ -1909,21 +1915,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>78</v>
@@ -1932,21 +1938,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>80</v>
@@ -1955,21 +1961,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>82</v>
@@ -1978,21 +1984,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>84</v>
@@ -2001,21 +2007,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>86</v>
@@ -2024,21 +2030,21 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>88</v>
@@ -2047,21 +2053,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>90</v>
@@ -2070,21 +2076,21 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>92</v>
@@ -2093,12 +2099,12 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>93</v>
@@ -2107,7 +2113,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>94</v>
@@ -2116,21 +2122,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>96</v>
@@ -2139,21 +2145,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>98</v>
@@ -2162,21 +2168,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>100</v>
@@ -2185,21 +2191,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>102</v>
@@ -2208,21 +2214,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>104</v>
@@ -2231,21 +2237,21 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>106</v>
@@ -2254,7 +2260,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="79">
@@ -2262,59 +2268,59 @@
         <v>109</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>110</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>48</v>
@@ -2323,21 +2329,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>50</v>
@@ -2346,21 +2352,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>52</v>
@@ -2369,21 +2375,21 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>54</v>
@@ -2392,21 +2398,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>56</v>
@@ -2415,21 +2421,21 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>58</v>
@@ -2438,21 +2444,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>60</v>
@@ -2461,21 +2467,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>62</v>
@@ -2484,21 +2490,21 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>64</v>
@@ -2507,21 +2513,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>66</v>
@@ -2530,21 +2536,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>68</v>
@@ -2553,21 +2559,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>70</v>
@@ -2576,21 +2582,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>72</v>
@@ -2599,21 +2605,21 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>74</v>
@@ -2622,21 +2628,21 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>76</v>
@@ -2645,21 +2651,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>78</v>
@@ -2668,21 +2674,21 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>80</v>
@@ -2691,21 +2697,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>82</v>
@@ -2714,21 +2720,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>84</v>
@@ -2737,21 +2743,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>86</v>
@@ -2760,21 +2766,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>88</v>
@@ -2783,21 +2789,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>90</v>
@@ -2806,21 +2812,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>92</v>
@@ -2829,21 +2835,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>94</v>
@@ -2852,21 +2858,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>96</v>
@@ -2875,21 +2881,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>98</v>
@@ -2898,7 +2904,7 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="107">
@@ -2906,82 +2912,82 @@
         <v>111</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>112</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>116</v>
@@ -2990,35 +2996,35 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>49</v>
@@ -3027,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>50</v>
@@ -3036,67 +3042,67 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>120</v>
@@ -3105,44 +3111,44 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>60</v>
@@ -3151,21 +3157,21 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>62</v>
@@ -3174,21 +3180,21 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>64</v>
@@ -3197,21 +3203,21 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>66</v>
@@ -3220,21 +3226,21 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>68</v>
@@ -3243,67 +3249,67 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>102</v>
@@ -3312,21 +3318,21 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>104</v>
@@ -3335,21 +3341,21 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>106</v>
@@ -3358,30 +3364,53 @@
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
